--- a/data/trans_dic/P16A15-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A15-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,52; 13,03</t>
+          <t>9,49; 13,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,42; 23,88</t>
+          <t>18,46; 23,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,05; 23,62</t>
+          <t>18,05; 23,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,73; 27,19</t>
+          <t>20,63; 26,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,58; 17,42</t>
+          <t>13,48; 17,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,17; 26,85</t>
+          <t>22,09; 26,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,74; 27,46</t>
+          <t>21,88; 27,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,28; 33,3</t>
+          <t>28,23; 32,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,23; 15,13</t>
+          <t>12,23; 14,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,32; 24,97</t>
+          <t>21,3; 24,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,87; 25,05</t>
+          <t>21,0; 25,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,95; 29,74</t>
+          <t>25,78; 29,77</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,14</t>
+          <t>2,45; 4,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 7,22</t>
+          <t>4,83; 7,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,41; 7,54</t>
+          <t>5,49; 7,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,4; 10,98</t>
+          <t>6,43; 10,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,34</t>
+          <t>2,53; 4,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 6,38</t>
+          <t>4,17; 6,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,28; 7,59</t>
+          <t>5,4; 7,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,67; 40,81</t>
+          <t>8,64; 40,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 3,9</t>
+          <t>2,66; 3,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,42</t>
+          <t>4,82; 6,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,61; 7,23</t>
+          <t>5,72; 7,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,82; 27,24</t>
+          <t>8,8; 25,96</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,54</t>
+          <t>2,16; 5,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 10,31</t>
+          <t>4,38; 9,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,18</t>
+          <t>3,19; 7,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,17; 11,28</t>
+          <t>7,0; 11,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,2</t>
+          <t>1,24; 4,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,96</t>
+          <t>2,11; 6,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,07</t>
+          <t>1,67; 5,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,42; 10,84</t>
+          <t>7,4; 10,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,35</t>
+          <t>2,07; 4,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 6,97</t>
+          <t>3,84; 7,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,31</t>
+          <t>2,83; 5,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,75; 10,4</t>
+          <t>7,65; 10,33</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,64</t>
+          <t>5,02; 6,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,17; 11,41</t>
+          <t>9,22; 11,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,33; 10,45</t>
+          <t>8,4; 10,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,93; 12,83</t>
+          <t>8,95; 12,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 8,8</t>
+          <t>6,98; 8,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,2; 13,5</t>
+          <t>11,2; 13,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,04; 12,25</t>
+          <t>9,97; 12,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,33; 32,25</t>
+          <t>13,4; 33,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 7,52</t>
+          <t>6,32; 7,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,52; 12,09</t>
+          <t>10,66; 12,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,48; 10,94</t>
+          <t>9,49; 10,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,31; 24,44</t>
+          <t>12,28; 25,91</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98260; 134419</t>
+          <t>97865; 137904</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>179519; 232769</t>
+          <t>179935; 230355</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>136190; 178191</t>
+          <t>136157; 179076</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106521; 139726</t>
+          <t>106008; 138626</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>178535; 229140</t>
+          <t>177276; 228612</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>295418; 357737</t>
+          <t>294338; 358142</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>216265; 273089</t>
+          <t>217632; 274203</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>212655; 250445</t>
+          <t>212310; 247691</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>287101; 354996</t>
+          <t>287072; 351147</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>491868; 576098</t>
+          <t>491334; 570908</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>365091; 438180</t>
+          <t>367290; 439261</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>328551; 376467</t>
+          <t>326402; 376858</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40220; 70013</t>
+          <t>41527; 70845</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>96868; 141479</t>
+          <t>94725; 138324</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>112272; 156580</t>
+          <t>114035; 157455</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>146676; 251505</t>
+          <t>147280; 251146</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39314; 68938</t>
+          <t>40150; 70549</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72922; 111752</t>
+          <t>72993; 114633</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>104965; 150893</t>
+          <t>107286; 152530</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>193926; 912898</t>
+          <t>193387; 900023</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86349; 128030</t>
+          <t>87406; 129325</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>180366; 238384</t>
+          <t>179038; 240425</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>228184; 293788</t>
+          <t>232468; 296538</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>399152; 1233283</t>
+          <t>398265; 1175496</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12661; 30553</t>
+          <t>11885; 30564</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22136; 49507</t>
+          <t>21056; 46643</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17324; 39289</t>
+          <t>17422; 40392</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46395; 72920</t>
+          <t>45238; 71487</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6011; 20028</t>
+          <t>5893; 19589</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9328; 27269</t>
+          <t>9640; 27481</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8581; 27817</t>
+          <t>9162; 28673</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>49020; 71571</t>
+          <t>48852; 72017</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21149; 44746</t>
+          <t>21284; 44545</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34579; 65336</t>
+          <t>36026; 66872</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30060; 58162</t>
+          <t>30973; 58836</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>101349; 135938</t>
+          <t>99977; 135008</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>164412; 217366</t>
+          <t>164340; 218178</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>313078; 389609</t>
+          <t>314818; 390895</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>281457; 352983</t>
+          <t>283691; 352219</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>308155; 442600</t>
+          <t>308974; 441809</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>238111; 297241</t>
+          <t>235995; 297745</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>396748; 478160</t>
+          <t>396812; 481977</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>354548; 432771</t>
+          <t>352046; 430903</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>486674; 1176976</t>
+          <t>489185; 1238434</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>413344; 500464</t>
+          <t>420869; 502330</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>731729; 841260</t>
+          <t>741186; 846611</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>655373; 755921</t>
+          <t>655392; 756046</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>873872; 1735370</t>
+          <t>871597; 1839774</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A15-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A15-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,49; 13,37</t>
+          <t>9,47; 13,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,46; 23,63</t>
+          <t>18,46; 23,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,05; 23,74</t>
+          <t>17,8; 23,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,63; 26,97</t>
+          <t>18,94; 25,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,48; 17,38</t>
+          <t>13,63; 17,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,09; 26,88</t>
+          <t>22,03; 26,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,88; 27,57</t>
+          <t>21,65; 27,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,23; 32,93</t>
+          <t>28,12; 33,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,23; 14,96</t>
+          <t>12,25; 15,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,3; 24,75</t>
+          <t>21,32; 24,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,0; 25,11</t>
+          <t>20,87; 25,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,78; 29,77</t>
+          <t>25,21; 29,05</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,19</t>
+          <t>2,4; 4,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 7,06</t>
+          <t>4,78; 7,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,49; 7,58</t>
+          <t>5,38; 7,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 10,97</t>
+          <t>9,21; 11,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,44</t>
+          <t>2,48; 4,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,54</t>
+          <t>4,21; 6,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 7,67</t>
+          <t>5,33; 7,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,64; 40,23</t>
+          <t>8,33; 10,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 3,94</t>
+          <t>2,62; 3,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 6,48</t>
+          <t>4,86; 6,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 7,3</t>
+          <t>5,7; 7,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,8; 25,96</t>
+          <t>9,03; 10,52</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,54</t>
+          <t>2,35; 5,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 9,71</t>
+          <t>4,56; 9,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 7,39</t>
+          <t>3,13; 7,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 11,06</t>
+          <t>7,24; 11,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,11</t>
+          <t>1,24; 4,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,0</t>
+          <t>2,05; 5,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,22</t>
+          <t>1,5; 4,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 10,9</t>
+          <t>7,68; 11,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,33</t>
+          <t>2,12; 4,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,13</t>
+          <t>3,58; 6,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,37</t>
+          <t>2,78; 5,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,65; 10,33</t>
+          <t>7,95; 10,59</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,66</t>
+          <t>5,02; 6,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,22; 11,45</t>
+          <t>9,27; 11,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,4; 10,43</t>
+          <t>8,45; 10,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,95; 12,8</t>
+          <t>11,11; 13,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 8,81</t>
+          <t>7,0; 8,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,2; 13,61</t>
+          <t>11,19; 13,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,97; 12,2</t>
+          <t>9,9; 12,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,4; 33,93</t>
+          <t>13,03; 14,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,32; 7,55</t>
+          <t>6,31; 7,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,66; 12,17</t>
+          <t>10,52; 12,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 10,94</t>
+          <t>9,47; 10,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,28; 25,91</t>
+          <t>12,29; 13,66</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>122507</t>
+          <t>127900</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>229759</t>
+          <t>250670</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>352266</t>
+          <t>378570</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97865; 137904</t>
+          <t>97750; 139075</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>179935; 230355</t>
+          <t>179888; 228528</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>136157; 179076</t>
+          <t>134299; 178566</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106008; 138626</t>
+          <t>109408; 145599</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>177276; 228612</t>
+          <t>179219; 231051</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>294338; 358142</t>
+          <t>293499; 357697</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>217632; 274203</t>
+          <t>215314; 272400</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>212310; 247691</t>
+          <t>230645; 271010</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>287072; 351147</t>
+          <t>287398; 352162</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>491334; 570908</t>
+          <t>491833; 574065</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>367290; 439261</t>
+          <t>365071; 437883</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>326402; 376858</t>
+          <t>352383; 406018</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>215004</t>
+          <t>230825</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>388742</t>
+          <t>199857</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>603746</t>
+          <t>430682</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41527; 70845</t>
+          <t>40634; 70581</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>94725; 138324</t>
+          <t>93699; 138755</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>114035; 157455</t>
+          <t>111740; 158566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>147280; 251146</t>
+          <t>205531; 259567</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40150; 70549</t>
+          <t>39306; 69467</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72993; 114633</t>
+          <t>73794; 113337</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>107286; 152530</t>
+          <t>106071; 153405</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>193387; 900023</t>
+          <t>180856; 223091</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>87406; 129325</t>
+          <t>85947; 128012</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>179038; 240425</t>
+          <t>180317; 240398</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>232468; 296538</t>
+          <t>231695; 298504</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>398265; 1175496</t>
+          <t>397368; 463089</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57795</t>
+          <t>64160</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59907</t>
+          <t>67802</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>117702</t>
+          <t>131963</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11885; 30564</t>
+          <t>12933; 30828</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21056; 46643</t>
+          <t>21907; 47202</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17422; 40392</t>
+          <t>17108; 38413</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45238; 71487</t>
+          <t>51525; 79276</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5893; 19589</t>
+          <t>5929; 19411</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9640; 27481</t>
+          <t>9365; 27212</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9162; 28673</t>
+          <t>8218; 27038</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>48852; 72017</t>
+          <t>56430; 81394</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21284; 44545</t>
+          <t>21814; 42975</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36026; 66872</t>
+          <t>33536; 65202</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30973; 58836</t>
+          <t>30500; 58763</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>99977; 135008</t>
+          <t>114961; 153200</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>395306</t>
+          <t>422886</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>678408</t>
+          <t>518329</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1073714</t>
+          <t>941215</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>164340; 218178</t>
+          <t>164565; 216536</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>314818; 390895</t>
+          <t>316328; 388797</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>283691; 352219</t>
+          <t>285355; 353971</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>308974; 441809</t>
+          <t>390869; 461618</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>235995; 297745</t>
+          <t>236389; 297601</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>396812; 481977</t>
+          <t>396492; 476944</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>352046; 430903</t>
+          <t>349796; 429451</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>489185; 1238434</t>
+          <t>485388; 550491</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>420869; 502330</t>
+          <t>419808; 496259</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>741186; 846611</t>
+          <t>731998; 839881</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>655392; 756046</t>
+          <t>654641; 758025</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>871597; 1839774</t>
+          <t>890502; 989872</t>
         </is>
       </c>
     </row>
